--- a/pages/shp/uploads/000027BSV61820260921912982.xlsx
+++ b/pages/shp/uploads/000027BSV61820260921912982.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EXIM\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A4D64A-572D-416C-9ADD-6148C31EE9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4563EB38-C349-4698-A511-CBAAB142DD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
